--- a/tests/testthat/xlsx_files/reference_tables.xlsx
+++ b/tests/testthat/xlsx_files/reference_tables.xlsx
@@ -4843,19 +4843,19 @@
         <v>19.7462225964812</v>
       </c>
       <c r="C4" s="44" t="n">
-        <v>3.75970879742794</v>
+        <v>3.76</v>
       </c>
       <c r="D4" s="45" t="n">
-        <v>0.000765046639878853</v>
+        <v>0.001</v>
       </c>
       <c r="E4" s="46" t="n">
         <v>19.7462225964812</v>
       </c>
       <c r="F4" s="47" t="n">
-        <v>3.75970879742794</v>
+        <v>3.76</v>
       </c>
       <c r="G4" s="48" t="n">
-        <v>0.000765046639878853</v>
+        <v>0.001</v>
       </c>
       <c r="H4" s="14"/>
     </row>
@@ -4867,19 +4867,19 @@
         <v>-5.04798198284328</v>
       </c>
       <c r="C5" s="44" t="n">
-        <v>-10.429770825164</v>
+        <v>-10.43</v>
       </c>
       <c r="D5" s="45" t="n">
-        <v>0.0000000000251894849832309</v>
+        <v>0</v>
       </c>
       <c r="E5" s="46" t="n">
         <v>-5.04798198284328</v>
       </c>
       <c r="F5" s="47" t="n">
-        <v>-10.429770825164</v>
+        <v>-10.43</v>
       </c>
       <c r="G5" s="48" t="n">
-        <v>0.0000000000251894849832309</v>
+        <v>0</v>
       </c>
       <c r="H5" s="14"/>
     </row>
@@ -4891,19 +4891,19 @@
         <v>0.929197979568393</v>
       </c>
       <c r="C6" s="44" t="n">
-        <v>3.50617865987038</v>
+        <v>3.506</v>
       </c>
       <c r="D6" s="45" t="n">
-        <v>0.00149988281008463</v>
+        <v>0.001</v>
       </c>
       <c r="E6" s="46" t="n">
         <v>0.929197979568393</v>
       </c>
       <c r="F6" s="47" t="n">
-        <v>3.50617865987038</v>
+        <v>3.506</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>0.00149988281008463</v>
+        <v>0.001</v>
       </c>
       <c r="H6" s="14"/>
     </row>
